--- a/光伏配储项目/电价数据/2026/鲲鹏站.xlsx
+++ b/光伏配储项目/电价数据/2026/鲲鹏站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.32129</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.5131</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58933</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.09340999999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44103</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45843</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42545</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41194</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41563</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41656</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42667</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41439</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.50016</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.11828</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.12996</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13673</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.06798999999999999</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10859</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.6322300000000001</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.22363</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28629</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.65161</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.00234</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1471</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21824</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22865</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23375</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21788</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.5824</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14454</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.6043099999999999</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.7360800000000001</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.8264400000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.6299199999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73117</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.23661</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39447</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43126</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43654</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65838</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.04221</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.6502100000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.37819</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.23263</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.61778</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.86139</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.9211699999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.40281</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8727200000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7966599999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75722</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51716</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47972</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46837</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42548</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70892</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.7751</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.87249</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91764</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.4948</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51522</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50296</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50319</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48545</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4675299999999999</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.88924</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.82765</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45786</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.44012</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5086000000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.42841</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50136</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.77185</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9855900000000001</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.87979</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.83736</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.49007</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.71739</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.17952</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.05858</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.01423</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.46575</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5424099999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.4947</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.51889</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.94012</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.61948</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.01592</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.52277</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.69046</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17238</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.22016</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.73635</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.63852</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.79383</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.57127</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.62337</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.18058</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.51592</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90291</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.62426</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.77427</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.50192</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.27311</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45021</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78476</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80661</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44912</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42823</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44371</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33462</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48715</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48718</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44717</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44331</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44404</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43803</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.55943</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.81304</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.04114</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.9226599999999999</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.86595</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.25954</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.39573</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5468</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.48675</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8076599999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.58325</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7173999999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8065399999999999</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5243099999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.55568</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7970900000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.34515</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6866</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.59336</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49276</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42547</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.85799</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5025500000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5696</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59429</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.53975</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.55937</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26605</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61661</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.76349</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5448500000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.58657</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.09714</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.19096</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.40066</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.04135</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.95639</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.76462</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.08684</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6107100000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.99434</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56248</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.50337</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.95114</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.55787</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.47942</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6132300000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.53135</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45681</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34198</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52078</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49442</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44384</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44879</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39358</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41631</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.5610499999999999</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.88722</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.74779</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>1.0562</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.50381</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.96366</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>1.16873</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.77198</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.8435199999999999</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.67487</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.51328</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.42417</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.32038</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>1.17421</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.46892</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60592</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.44611</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47848</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.18916</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>1.18712</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.02575</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.65652</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42962</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49624</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46212</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47437</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51874</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.19988</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.11252</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.7865</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.1919</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.04651</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50112</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.95389</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.89266</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.7443</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.6234</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.6112799999999999</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31774</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7925099999999999</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.9497599999999999</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.46084</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.19247</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.27873</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.21389</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14992</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.06522</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.25016</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18805</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.04318</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22327</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.24956</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.20669</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06264</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.02109</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.00877</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00167</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.9896900000000001</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26724</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46242</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48893</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.60149</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.39463</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1027</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04353</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01425</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21428</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05328</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.28732</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20044</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.05598</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.05519</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06842000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06665</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33222</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31388</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38626</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42769</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45556</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38718</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78525</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29621</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87388</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.9017500000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33085</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03291</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.60821</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39989</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20699</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62185</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44969</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38381</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41027</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42793</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44958</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5642999999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41604</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5867899999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.71347</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87727</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46692</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55786</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43744</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.82896</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5817899999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8542000000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87499</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.42253</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.6423099999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.64078</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59193</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.60829</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42811</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34836</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9146599999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44757</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.44214</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.46834</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28862</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.18553</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30428</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27308</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19797</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29878</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28175</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25406</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27478</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41761</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.47805</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44187</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.40387</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.54434</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8705900000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44461</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14292</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6889299999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7793300000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6406000000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.51842</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.40949</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44201</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49204</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43215</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.42006</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40701</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.4693</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40628</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42696</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.40467</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.42337</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41749</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.41028</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.3992</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48811</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.52873</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.24142</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24858</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15477</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27492</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01195</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26021</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2534</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28194</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.54741</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43811</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7969700000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43951</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44324</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.31026</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.25663</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.26004</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2487</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26739</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22846</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.20272</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.25038</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.27287</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.19906</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.21771</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.25172</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.26966</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.23422</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.28237</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.19581</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.21891</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.25905</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.20191</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.25673</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.21852</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.42395</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.42771</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.41553</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43912</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33757</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.50132</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.44254</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4045899999999999</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.42593</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.84838</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>1.04907</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.42407</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25035</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27697</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29718</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23981</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.63405</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.6896100000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60997</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.45154</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.03979</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.10628</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.43605</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>1.06551</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.38235</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.9146599999999999</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.42258</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.46419</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.46376</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.45714</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.8451900000000001</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.5268400000000001</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35117</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4701</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.48246</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.56641</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.66401</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.64898</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.60765</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.59054</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.42193</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.09317</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.6725</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.65599</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.05551</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.62625</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.25695</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.1293</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.16583</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.57651</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.88327</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.05781</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.63928</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.6706</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.28791</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.62123</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.65883</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.34659</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.69383</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.22126</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.90071</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.5896</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.90924</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.8751599999999999</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.96417</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.88966</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.88587</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.52018</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.01249</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.9929199999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.9748300000000001</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.24935</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.92159</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.68068</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.6270399999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.53135</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24257</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.02093</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31755</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.20976</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41381</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.23818</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.54698</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>1.01461</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.44253</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.66037</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.33377</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.5805399999999999</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>1.06696</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.40296</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>1.0673</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34456</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.8228799999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.48404</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.58589</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.44235</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.43274</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.63373</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.40069</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.44064</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.48252</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.42575</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.55086</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.44601</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41034</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.69731</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65196</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.43327</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.82556</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.68469</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>1.00588</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.7854800000000001</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33644</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40601</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.5289299999999999</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>1.05114</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.6758500000000001</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>1.17101</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.52951</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.80516</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.23106</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.83043</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37405</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.4774</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.8959199999999999</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.6525299999999999</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>1.10622</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.9292100000000001</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.66823</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.8561</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.8346699999999999</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.17564</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.86502</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.17176</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.76743</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.71548</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.74495</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.16703</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.12483</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.67501</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>1.06101</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.19718</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.07624</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.01153</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.92289</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.726</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.8750599999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35292</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4623</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5384</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48303</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6324099999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39549</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.42199</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5156900000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.46823</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.42717</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.46489</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42556</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.63059</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.52348</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.14159</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.5707</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.60732</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.68711</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.26924</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.26949</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.10233</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.17817</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.20936</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.20047</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.27975</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.52901</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.58558</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.91927</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.25341</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.2506</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.24345</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.24504</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.00771</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37435</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39724</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41812</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.46574</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42674</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.48101</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.48131</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.51603</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.64001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7541</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.8452000000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.60766</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7330099999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.51712</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.2784700000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.75467</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7662</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6190599999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66752</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.15024</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.45569</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.45161</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.44469</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40173</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5157999999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41056</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.42207</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.43335</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41938</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.42441</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.41635</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36741</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.22949</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.22794</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.24674</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.23585</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.18472</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.24783</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.14495</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.21236</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.25804</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42663</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41246</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.43012</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.4030899999999999</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39779</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.33965</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.46873</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.00484</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.28312</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.27508</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.27409</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.26548</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.19632</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24207</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27563</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25929</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.2558</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.10646</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25585</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03629</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.18922</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.16676</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24593</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26648</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25922</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27773</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.28746</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.27212</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25037</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.32957</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.12915</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.28572</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.25589</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29861</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.26361</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.25589</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.25803</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.25802</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.25461</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.25461</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.25666</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28749</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.25181</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.25461</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.25494</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.2883</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.25605</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.25582</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17532</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26847</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.22271</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01386</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00013</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14641</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02139</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01532</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04288</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04077</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04859</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02926</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04914</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27488</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03806</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03609</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20189</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26522</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28874</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25959</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.42677</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.33585</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.75885</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.65338</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.45116</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.4215</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.43315</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.2641</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25484</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.24021</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2595</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.28359</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43832</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.28433</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.72075</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.86699</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85272</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11012</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.22572</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26614</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.03348</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.2595</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27135</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.007820000000000001</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27417</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.00364</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.05751</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47145</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.52659</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.79787</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.75041</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.7757500000000001</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.35536</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97104</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.7739299999999999</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.83913</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.80987</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84124</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83945</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84374</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94089</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.77167</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.8058200000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7742899999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36661</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.47332</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.62421</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.69656</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.58524</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49487</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.46974</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.48423</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.46965</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.4834</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.43228</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.45911</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.41153</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39526</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26051</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39791</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.41444</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.45354</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.72465</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.59553</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.45738</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42257</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.41625</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.48154</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34113</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42793</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.4117</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.56765</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.7758700000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.5483300000000001</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.48466</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.55859</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.25285</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.23792</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.24851</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.19334</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.22768</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>-0.009779999999999999</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.23893</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47007</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.6502100000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.11509</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.02879</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.62103</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.06893000000000001</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.71324</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.56212</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.46449</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.46292</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.26262</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.10662</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.04745000000000001</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.26574</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.42652</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38396</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23735</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35493</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37357</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43488</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.20225</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.12537</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.24665</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.18731</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41481</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51076</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.7139099999999999</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.16039</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.62234</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47758</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.59929</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.79796</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.69359</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.61971</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.76936</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.16941</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.26419</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3593</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.25043</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.26848</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.13934</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.17538</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.00749</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.14373</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.11334</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.23587</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.13995</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.1605</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.24044</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.00321</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.20865</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.23543</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.22822</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.25385</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>-0.01386</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43592</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.23497</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.27143</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.23706</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.00564</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40996</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37159</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.24908</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36633</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.7714099999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.07235999999999999</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5591799999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.03309</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44245</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.43776</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28038</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.12519</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.2561</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40617</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.27349</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.1986</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.2567</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.25436</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>-0.0451</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.25656</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.24651</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.10459</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.16015</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.26039</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36013</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38646</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17567</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14534</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19805</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14175</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04473</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.1207</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22476</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.2633</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14963</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14346</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19438</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.2262</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26243</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15318</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15336</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19693</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14298</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.28008</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.13344</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.22181</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>-0.01764</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.15081</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.25009</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.22793</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.43998</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38546</v>
       </c>
     </row>
   </sheetData>
